--- a/artfynd/A 2054-2024 artfynd.xlsx
+++ b/artfynd/A 2054-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,127 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114729890</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56083</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fjällboheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>749912</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7217119</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2054-2024 artfynd.xlsx
+++ b/artfynd/A 2054-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2054-2024 artfynd.xlsx
+++ b/artfynd/A 2054-2024 artfynd.xlsx
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119536128</v>
+        <v>119536567</v>
       </c>
       <c r="B5" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,21 +1038,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750071</v>
+        <v>749951</v>
       </c>
       <c r="R5" t="n">
-        <v>7217287</v>
+        <v>7217195</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536567</v>
+        <v>119536128</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>749951</v>
+        <v>750071</v>
       </c>
       <c r="R6" t="n">
-        <v>7217195</v>
+        <v>7217287</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2702,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536418</v>
+        <v>119536543</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>96868</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,21 +2718,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>749986</v>
+        <v>750092</v>
       </c>
       <c r="R20" t="n">
-        <v>7217300</v>
+        <v>7217107</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119537165</v>
+        <v>119536564</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>749944</v>
+        <v>750090</v>
       </c>
       <c r="R21" t="n">
-        <v>7217199</v>
+        <v>7217089</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536564</v>
+        <v>119536418</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2938,25 +2938,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750090</v>
+        <v>749986</v>
       </c>
       <c r="R22" t="n">
-        <v>7217089</v>
+        <v>7217300</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536543</v>
+        <v>119537165</v>
       </c>
       <c r="B23" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,25 +3050,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750092</v>
+        <v>749944</v>
       </c>
       <c r="R23" t="n">
-        <v>7217107</v>
+        <v>7217199</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 2054-2024 artfynd.xlsx
+++ b/artfynd/A 2054-2024 artfynd.xlsx
@@ -2702,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536543</v>
+        <v>119536418</v>
       </c>
       <c r="B20" t="n">
-        <v>96868</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,21 +2718,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750092</v>
+        <v>749986</v>
       </c>
       <c r="R20" t="n">
-        <v>7217107</v>
+        <v>7217300</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536564</v>
+        <v>119537165</v>
       </c>
       <c r="B21" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750090</v>
+        <v>749944</v>
       </c>
       <c r="R21" t="n">
-        <v>7217089</v>
+        <v>7217199</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536418</v>
+        <v>119536564</v>
       </c>
       <c r="B22" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2938,25 +2938,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>749986</v>
+        <v>750090</v>
       </c>
       <c r="R22" t="n">
-        <v>7217300</v>
+        <v>7217089</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119537165</v>
+        <v>119536543</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,25 +3050,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>749944</v>
+        <v>750092</v>
       </c>
       <c r="R23" t="n">
-        <v>7217199</v>
+        <v>7217107</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 2054-2024 artfynd.xlsx
+++ b/artfynd/A 2054-2024 artfynd.xlsx
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119536567</v>
+        <v>119537058</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,25 +1034,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749951</v>
+        <v>750109</v>
       </c>
       <c r="R5" t="n">
-        <v>7217195</v>
+        <v>7217063</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119536128</v>
+        <v>119536564</v>
       </c>
       <c r="B6" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750071</v>
+        <v>750090</v>
       </c>
       <c r="R6" t="n">
-        <v>7217287</v>
+        <v>7217089</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119537058</v>
+        <v>119536128</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,25 +1258,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750109</v>
+        <v>750071</v>
       </c>
       <c r="R7" t="n">
-        <v>7217063</v>
+        <v>7217287</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536127</v>
+        <v>119536548</v>
       </c>
       <c r="B8" t="n">
-        <v>91463</v>
+        <v>96868</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,25 +1370,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4745</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>749968</v>
+        <v>750174</v>
       </c>
       <c r="R8" t="n">
-        <v>7217282</v>
+        <v>7217072</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536546</v>
+        <v>119537160</v>
       </c>
       <c r="B9" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,25 +1482,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750185</v>
+        <v>750064</v>
       </c>
       <c r="R9" t="n">
-        <v>7217166</v>
+        <v>7217132</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119537158</v>
+        <v>119536545</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,25 +1594,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750140</v>
+        <v>750166</v>
       </c>
       <c r="R10" t="n">
-        <v>7217016</v>
+        <v>7217148</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,7 +1694,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119537163</v>
+        <v>119537162</v>
       </c>
       <c r="B11" t="n">
         <v>91834</v>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>749959</v>
+        <v>749978</v>
       </c>
       <c r="R11" t="n">
-        <v>7217193</v>
+        <v>7217160</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536126</v>
+        <v>119537169</v>
       </c>
       <c r="B12" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750099</v>
+        <v>749974</v>
       </c>
       <c r="R12" t="n">
-        <v>7217045</v>
+        <v>7217281</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,7 +1918,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537170</v>
+        <v>119537166</v>
       </c>
       <c r="B13" t="n">
         <v>91834</v>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750070</v>
+        <v>749911</v>
       </c>
       <c r="R13" t="n">
-        <v>7217288</v>
+        <v>7217230</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537172</v>
+        <v>119537165</v>
       </c>
       <c r="B14" t="n">
         <v>91834</v>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750160</v>
+        <v>749944</v>
       </c>
       <c r="R14" t="n">
-        <v>7217096</v>
+        <v>7217199</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536569</v>
+        <v>119536127</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750086</v>
+        <v>749968</v>
       </c>
       <c r="R15" t="n">
-        <v>7217284</v>
+        <v>7217282</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536419</v>
+        <v>119537170</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,25 +2266,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750014</v>
+        <v>750070</v>
       </c>
       <c r="R16" t="n">
-        <v>7217335</v>
+        <v>7217288</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536548</v>
+        <v>119537164</v>
       </c>
       <c r="B17" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,25 +2378,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750174</v>
+        <v>749968</v>
       </c>
       <c r="R17" t="n">
-        <v>7217072</v>
+        <v>7217180</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119537164</v>
+        <v>119536126</v>
       </c>
       <c r="B18" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2494,21 +2494,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>749968</v>
+        <v>750099</v>
       </c>
       <c r="R18" t="n">
-        <v>7217180</v>
+        <v>7217045</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2590,7 +2590,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119537167</v>
+        <v>119537161</v>
       </c>
       <c r="B19" t="n">
         <v>91834</v>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>749899</v>
+        <v>750015</v>
       </c>
       <c r="R19" t="n">
-        <v>7217236</v>
+        <v>7217110</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536418</v>
+        <v>119537159</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2714,25 +2714,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>749986</v>
+        <v>750091</v>
       </c>
       <c r="R20" t="n">
-        <v>7217300</v>
+        <v>7217088</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119537165</v>
+        <v>119536546</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2826,25 +2826,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>749944</v>
+        <v>750185</v>
       </c>
       <c r="R21" t="n">
-        <v>7217199</v>
+        <v>7217166</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536564</v>
+        <v>119537158</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750090</v>
+        <v>750140</v>
       </c>
       <c r="R22" t="n">
-        <v>7217089</v>
+        <v>7217016</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536543</v>
+        <v>119536569</v>
       </c>
       <c r="B23" t="n">
-        <v>96868</v>
+        <v>91832</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,25 +3050,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750092</v>
+        <v>750086</v>
       </c>
       <c r="R23" t="n">
-        <v>7217107</v>
+        <v>7217284</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536566</v>
+        <v>119536419</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3162,25 +3162,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750084</v>
+        <v>750014</v>
       </c>
       <c r="R24" t="n">
-        <v>7217095</v>
+        <v>7217335</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,10 +3262,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536257</v>
+        <v>119537059</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3274,25 +3274,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750160</v>
+        <v>750163</v>
       </c>
       <c r="R25" t="n">
-        <v>7217096</v>
+        <v>7217146</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536115</v>
+        <v>119536566</v>
       </c>
       <c r="B26" t="n">
-        <v>91826</v>
+        <v>91832</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3390,21 +3390,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750071</v>
+        <v>750084</v>
       </c>
       <c r="R26" t="n">
-        <v>7217287</v>
+        <v>7217095</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,10 +3486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119537162</v>
+        <v>119536115</v>
       </c>
       <c r="B27" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3502,21 +3502,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>749978</v>
+        <v>750071</v>
       </c>
       <c r="R27" t="n">
-        <v>7217160</v>
+        <v>7217287</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,7 +3598,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119537166</v>
+        <v>119537168</v>
       </c>
       <c r="B28" t="n">
         <v>91834</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>749911</v>
+        <v>749902</v>
       </c>
       <c r="R28" t="n">
-        <v>7217230</v>
+        <v>7217245</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,10 +3710,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119537168</v>
+        <v>119536543</v>
       </c>
       <c r="B29" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3722,25 +3722,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>749902</v>
+        <v>750092</v>
       </c>
       <c r="R29" t="n">
-        <v>7217245</v>
+        <v>7217107</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,10 +3822,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119537059</v>
+        <v>119537172</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3834,25 +3834,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>750163</v>
+        <v>750160</v>
       </c>
       <c r="R30" t="n">
-        <v>7217146</v>
+        <v>7217096</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,7 +3934,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119537169</v>
+        <v>119537167</v>
       </c>
       <c r="B31" t="n">
         <v>91834</v>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>749974</v>
+        <v>749899</v>
       </c>
       <c r="R31" t="n">
-        <v>7217281</v>
+        <v>7217236</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,7 +4046,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119537161</v>
+        <v>119537163</v>
       </c>
       <c r="B32" t="n">
         <v>91834</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>750015</v>
+        <v>749959</v>
       </c>
       <c r="R32" t="n">
-        <v>7217110</v>
+        <v>7217193</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119537160</v>
+        <v>119536417</v>
       </c>
       <c r="B33" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>750064</v>
+        <v>749993</v>
       </c>
       <c r="R33" t="n">
-        <v>7217132</v>
+        <v>7217331</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,10 +4270,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119537159</v>
+        <v>119536257</v>
       </c>
       <c r="B34" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>750091</v>
+        <v>750160</v>
       </c>
       <c r="R34" t="n">
-        <v>7217088</v>
+        <v>7217096</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536417</v>
+        <v>119536567</v>
       </c>
       <c r="B35" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4394,25 +4394,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>749993</v>
+        <v>749951</v>
       </c>
       <c r="R35" t="n">
-        <v>7217331</v>
+        <v>7217195</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4494,10 +4494,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536545</v>
+        <v>119536418</v>
       </c>
       <c r="B36" t="n">
-        <v>96868</v>
+        <v>91852</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>750166</v>
+        <v>749986</v>
       </c>
       <c r="R36" t="n">
-        <v>7217148</v>
+        <v>7217300</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 2054-2024 artfynd.xlsx
+++ b/artfynd/A 2054-2024 artfynd.xlsx
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536545</v>
+        <v>119537162</v>
       </c>
       <c r="B10" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,25 +1594,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750166</v>
+        <v>749978</v>
       </c>
       <c r="R10" t="n">
-        <v>7217148</v>
+        <v>7217160</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119537162</v>
+        <v>119536545</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,25 +1706,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>749978</v>
+        <v>750166</v>
       </c>
       <c r="R11" t="n">
-        <v>7217160</v>
+        <v>7217148</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119537164</v>
+        <v>119536126</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2382,21 +2382,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>749968</v>
+        <v>750099</v>
       </c>
       <c r="R17" t="n">
-        <v>7217180</v>
+        <v>7217045</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536126</v>
+        <v>119537164</v>
       </c>
       <c r="B18" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2494,21 +2494,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750099</v>
+        <v>749968</v>
       </c>
       <c r="R18" t="n">
-        <v>7217045</v>
+        <v>7217180</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 2054-2024 artfynd.xlsx
+++ b/artfynd/A 2054-2024 artfynd.xlsx
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119537058</v>
+        <v>119536128</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,25 +1034,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750109</v>
+        <v>750071</v>
       </c>
       <c r="R5" t="n">
-        <v>7217063</v>
+        <v>7217287</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536128</v>
+        <v>119537160</v>
       </c>
       <c r="B7" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750071</v>
+        <v>750064</v>
       </c>
       <c r="R7" t="n">
-        <v>7217287</v>
+        <v>7217132</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536548</v>
+        <v>119537168</v>
       </c>
       <c r="B8" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,25 +1370,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750174</v>
+        <v>749902</v>
       </c>
       <c r="R8" t="n">
-        <v>7217072</v>
+        <v>7217245</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119537160</v>
+        <v>119536257</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750064</v>
+        <v>750160</v>
       </c>
       <c r="R9" t="n">
-        <v>7217132</v>
+        <v>7217096</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119537162</v>
+        <v>119536548</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,25 +1594,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>749978</v>
+        <v>750174</v>
       </c>
       <c r="R10" t="n">
-        <v>7217160</v>
+        <v>7217072</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536545</v>
+        <v>119537170</v>
       </c>
       <c r="B11" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,25 +1706,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750166</v>
+        <v>750070</v>
       </c>
       <c r="R11" t="n">
-        <v>7217148</v>
+        <v>7217288</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,7 +1806,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119537169</v>
+        <v>119537159</v>
       </c>
       <c r="B12" t="n">
         <v>91834</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>749974</v>
+        <v>750091</v>
       </c>
       <c r="R12" t="n">
-        <v>7217281</v>
+        <v>7217088</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537166</v>
+        <v>119536419</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,25 +1930,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>749911</v>
+        <v>750014</v>
       </c>
       <c r="R13" t="n">
-        <v>7217230</v>
+        <v>7217335</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537165</v>
+        <v>119537161</v>
       </c>
       <c r="B14" t="n">
         <v>91834</v>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>749944</v>
+        <v>750015</v>
       </c>
       <c r="R14" t="n">
-        <v>7217199</v>
+        <v>7217110</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536127</v>
+        <v>119537169</v>
       </c>
       <c r="B15" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,21 +2158,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>749968</v>
+        <v>749974</v>
       </c>
       <c r="R15" t="n">
-        <v>7217282</v>
+        <v>7217281</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537170</v>
+        <v>119537167</v>
       </c>
       <c r="B16" t="n">
         <v>91834</v>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750070</v>
+        <v>749899</v>
       </c>
       <c r="R16" t="n">
-        <v>7217288</v>
+        <v>7217236</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119536126</v>
+        <v>119536417</v>
       </c>
       <c r="B17" t="n">
-        <v>91463</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,25 +2378,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750099</v>
+        <v>749993</v>
       </c>
       <c r="R17" t="n">
-        <v>7217045</v>
+        <v>7217331</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119537164</v>
+        <v>119536546</v>
       </c>
       <c r="B18" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,25 +2490,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>749968</v>
+        <v>750185</v>
       </c>
       <c r="R18" t="n">
-        <v>7217180</v>
+        <v>7217166</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2590,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119537161</v>
+        <v>119536115</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2606,21 +2606,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750015</v>
+        <v>750071</v>
       </c>
       <c r="R19" t="n">
-        <v>7217110</v>
+        <v>7217287</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,10 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119537159</v>
+        <v>119536127</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2718,21 +2718,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750091</v>
+        <v>749968</v>
       </c>
       <c r="R20" t="n">
-        <v>7217088</v>
+        <v>7217282</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536546</v>
+        <v>119537163</v>
       </c>
       <c r="B21" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2826,25 +2826,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750185</v>
+        <v>749959</v>
       </c>
       <c r="R21" t="n">
-        <v>7217166</v>
+        <v>7217193</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119537158</v>
+        <v>119536418</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2938,25 +2938,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750140</v>
+        <v>749986</v>
       </c>
       <c r="R22" t="n">
-        <v>7217016</v>
+        <v>7217300</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119536569</v>
+        <v>119536126</v>
       </c>
       <c r="B23" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3054,21 +3054,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750086</v>
+        <v>750099</v>
       </c>
       <c r="R23" t="n">
-        <v>7217284</v>
+        <v>7217045</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,10 +3150,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536419</v>
+        <v>119536545</v>
       </c>
       <c r="B24" t="n">
-        <v>91852</v>
+        <v>96868</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750014</v>
+        <v>750166</v>
       </c>
       <c r="R24" t="n">
-        <v>7217335</v>
+        <v>7217148</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,10 +3262,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119537059</v>
+        <v>119537172</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3274,25 +3274,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750163</v>
+        <v>750160</v>
       </c>
       <c r="R25" t="n">
-        <v>7217146</v>
+        <v>7217096</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536566</v>
+        <v>119537166</v>
       </c>
       <c r="B26" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3390,21 +3390,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750084</v>
+        <v>749911</v>
       </c>
       <c r="R26" t="n">
-        <v>7217095</v>
+        <v>7217230</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3486,10 +3486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536115</v>
+        <v>119537162</v>
       </c>
       <c r="B27" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3502,21 +3502,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>750071</v>
+        <v>749978</v>
       </c>
       <c r="R27" t="n">
-        <v>7217287</v>
+        <v>7217160</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3598,7 +3598,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119537168</v>
+        <v>119537158</v>
       </c>
       <c r="B28" t="n">
         <v>91834</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>749902</v>
+        <v>750140</v>
       </c>
       <c r="R28" t="n">
-        <v>7217245</v>
+        <v>7217016</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3710,10 +3710,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536543</v>
+        <v>119537164</v>
       </c>
       <c r="B29" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3722,25 +3722,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>750092</v>
+        <v>749968</v>
       </c>
       <c r="R29" t="n">
-        <v>7217107</v>
+        <v>7217180</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3822,7 +3822,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119537172</v>
+        <v>119537165</v>
       </c>
       <c r="B30" t="n">
         <v>91834</v>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>750160</v>
+        <v>749944</v>
       </c>
       <c r="R30" t="n">
-        <v>7217096</v>
+        <v>7217199</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119537167</v>
+        <v>119537058</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3946,25 +3946,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>749899</v>
+        <v>750109</v>
       </c>
       <c r="R31" t="n">
-        <v>7217236</v>
+        <v>7217063</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119537163</v>
+        <v>119536567</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>749959</v>
+        <v>749951</v>
       </c>
       <c r="R32" t="n">
-        <v>7217193</v>
+        <v>7217195</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536417</v>
+        <v>119537059</v>
       </c>
       <c r="B33" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>749993</v>
+        <v>750163</v>
       </c>
       <c r="R33" t="n">
-        <v>7217331</v>
+        <v>7217146</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,10 +4270,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536257</v>
+        <v>119536566</v>
       </c>
       <c r="B34" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>750160</v>
+        <v>750084</v>
       </c>
       <c r="R34" t="n">
-        <v>7217096</v>
+        <v>7217095</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4382,7 +4382,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536567</v>
+        <v>119536569</v>
       </c>
       <c r="B35" t="n">
         <v>91832</v>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>749951</v>
+        <v>750086</v>
       </c>
       <c r="R35" t="n">
-        <v>7217195</v>
+        <v>7217284</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4494,10 +4494,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536418</v>
+        <v>119536543</v>
       </c>
       <c r="B36" t="n">
-        <v>91852</v>
+        <v>96868</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4510,21 +4510,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>749986</v>
+        <v>750092</v>
       </c>
       <c r="R36" t="n">
-        <v>7217300</v>
+        <v>7217107</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
